--- a/cache/sepidar_template.xlsx
+++ b/cache/sepidar_template.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\milad_repo\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55A8D904-0540-49C2-B5EF-703C34C88891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900CDB51-A727-43E7-A80F-B64474BCCAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F0C15D09-4078-4B38-81F5-3054FF0141CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{36123008-5182-46C5-B5AC-EB71498B8803}"/>
   </bookViews>
   <sheets>
     <sheet name="Test" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,11 +31,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>نوع قلم</t>
   </si>
   <si>
+    <t>فاكتور شماره</t>
+  </si>
+  <si>
+    <t>فاكتور تاريخ</t>
+  </si>
+  <si>
+    <t>فاكتور كد مشتري</t>
+  </si>
+  <si>
+    <t>فاكتور كد نوع فروش</t>
+  </si>
+  <si>
     <t>قلم فاكتور كد</t>
   </si>
   <si>
@@ -72,140 +84,74 @@
     <t>قلم فاكتور توضيحات</t>
   </si>
   <si>
+    <t>فاكتور نام مشتري</t>
+  </si>
+  <si>
+    <t>فاكتور محل  تحويل</t>
+  </si>
+  <si>
     <t>قلم فاكتور تخفيف مشتري</t>
   </si>
   <si>
     <t>قلم فاكتور تخفيف درصدي اعلاميه قيمت</t>
   </si>
   <si>
-    <t>فاكتور عوامل افزاينده موثر بر ماليات بر ارزش افزوده</t>
-  </si>
-  <si>
-    <t>فاكتور محل تحويل (2)</t>
-  </si>
-  <si>
-    <t>فاكتور ماليات</t>
-  </si>
-  <si>
-    <t>فاكتور اضافات</t>
+    <t>فاكتور ارز1</t>
+  </si>
+  <si>
+    <t>فاكتور نرخ ارز</t>
+  </si>
+  <si>
+    <t>فاكتور نوع تسويه</t>
   </si>
   <si>
     <t>فاكتور تخفيف</t>
   </si>
   <si>
-    <t>فاكتور گروه مشتري</t>
+    <t>واسط مبلغ پورسانت</t>
+  </si>
+  <si>
+    <t>واسط كد واسط</t>
+  </si>
+  <si>
+    <t>واسط تفصيلي واسط</t>
   </si>
   <si>
     <t>فاكتور كل</t>
   </si>
   <si>
-    <t>فاكتور كد معين</t>
-  </si>
-  <si>
-    <t>فاكتور نوع فروش (2)</t>
-  </si>
-  <si>
-    <t>فاكتور نوع فروش1</t>
-  </si>
-  <si>
-    <t>فاكتور نوع فروش</t>
-  </si>
-  <si>
-    <t>فاكتور نام مشتري</t>
-  </si>
-  <si>
-    <t>فاكتور تاريخ</t>
-  </si>
-  <si>
-    <t>فاكتور مشتري</t>
-  </si>
-  <si>
-    <t>فاكتور شماره</t>
-  </si>
-  <si>
-    <t>فاكتور توضيحات</t>
-  </si>
-  <si>
-    <t>فاكتور صادر كننده فاكتور</t>
-  </si>
-  <si>
-    <t>فاكتور شماره تلفن مشتري</t>
+    <t>InvoiceItem</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>آدرس مشتري</t>
+  </si>
+  <si>
+    <t>ريال</t>
+  </si>
+  <si>
+    <t>واسط واسط</t>
   </si>
   <si>
     <t>اطلاعات مبالغ دريافتي فاكتور مبلغ حواله</t>
   </si>
   <si>
-    <t>اطلاعات مبالغ دريافتي فاكتور مبلغ كارتخوان</t>
-  </si>
-  <si>
     <t>اطلاعات مبالغ دريافتي فاكتور مبلغ نقد</t>
-  </si>
-  <si>
-    <t>اطلاعات مبالغ دريافتي فاكتور تخفيف نقدي</t>
-  </si>
-  <si>
-    <t>اطلاعات مبالغ دريافتي فاكتور فاكتور</t>
-  </si>
-  <si>
-    <t>اطلاعات مبالغ دريافتي فاكتور شناسه</t>
-  </si>
-  <si>
-    <t>اطلاعات مبالغ دريافتي فاكتور شماره پيگيري كارتخوان</t>
-  </si>
-  <si>
-    <t>اطلاعات مبالغ دريافتي فاكتور تسويه حساب طرف مقابل</t>
-  </si>
-  <si>
-    <t>درصد سهم واسط درصد سهم</t>
-  </si>
-  <si>
-    <t>درصد سهم واسط تفصيلي واسط</t>
-  </si>
-  <si>
-    <t>درصد سهم واسط واسط(2)</t>
-  </si>
-  <si>
-    <t>درصد سهم واسط واسط1</t>
-  </si>
-  <si>
-    <t>درصد سهم واسط واسط</t>
-  </si>
-  <si>
-    <t>درصد سهم واسط فاكتور</t>
-  </si>
-  <si>
-    <t>درصد سهم واسط شناسه</t>
-  </si>
-  <si>
-    <t>درصد سهم واسط مبلغ پورسانت دستي</t>
-  </si>
-  <si>
-    <t>درصد سهم واسط كد واسط</t>
-  </si>
-  <si>
-    <t>واسط مبلغ پورسانت</t>
-  </si>
-  <si>
-    <t>واسط نرخ</t>
-  </si>
-  <si>
-    <t>واسط نرخ پورسانت</t>
-  </si>
-  <si>
-    <t>واسط تفصيلي واسط</t>
-  </si>
-  <si>
-    <t>واسط كد واسط</t>
-  </si>
-  <si>
-    <t>فاكتور كد مشتري</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -214,8 +160,12 @@
       <sz val="10"/>
       <name val="Tahoma"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -225,6 +175,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -243,12 +199,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -267,9 +219,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -277,39 +229,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -361,7 +313,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -413,7 +365,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -472,6 +424,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -480,13 +439,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -551,45 +503,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CE57AC7-DF65-42DC-9A19-C2347A739D66}">
-  <dimension ref="A1:BD1"/>
-  <sheetFormatPr defaultColWidth="26" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3A2267-0A96-41D4-B659-3368E5D3D318}">
+  <dimension ref="A1:AF10"/>
+  <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="26" style="2"/>
+    <col min="31" max="32" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -678,88 +610,146 @@
         <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W2" s="2">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
+      <c r="Y2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC2" s="2"/>
+      <c r="AE2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF6" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF8" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AE10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF10" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="0" firstPageNumber="0" fitToWidth="0" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
